--- a/engagement_survey_forms/013_discipline_and_guidance_policy_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/013_discipline_and_guidance_policy_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Policy Awareness</t>
+          <t>What is the current level of policy awareness among employees in your team/department?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Policy Effectiveness</t>
+          <t>How effective do you think the policy is in its current form?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Improvement Ideas</t>
+          <t>Do you have any improvement ideas for the policy?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Do you have an email address that we can contact you at?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments_email</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comments and Email</t>
+          <t>What are your comments about this survey?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,178 +699,178 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comments_phone</t>
+          <t>communication_pref</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Comments and Phone</t>
+          <t>Do you have a preferred way of communication (e.g., email, phone, or in-person)?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>engagement_level</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>What is your level of engagement with the policy?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>What are your concerns or suggestions for the policy?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>policy_effectiveness_level</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>How effective do you think the policy is overall?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>comments_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Do you have any comments or feedback about the policy?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>policy_improvement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Do you have any suggestions for improvement?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,23 +883,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>comments_7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Comments 7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Any final comments?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_1}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 1}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_2}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 2}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,216 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_3}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 3}</t>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>policy_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>very_effective</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Very Effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>policy_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>somewhat_effective</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Somewhat Effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>policy_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>not_very_effective</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Not Very Effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>communication_pref_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>communication_pref_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>communication_pref_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>in-person</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>engagement_level_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>engagement_level_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>engagement_level_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>policy_effectiveness_level_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>very_effective</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Very Effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>policy_effectiveness_level_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>somewhat_effective</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Somewhat Effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>policy_effectiveness_level_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>not_very_effective</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not Very Effective</t>
         </is>
       </c>
     </row>
